--- a/assets/Lottery_Draw_Template.xlsx
+++ b/assets/Lottery_Draw_Template.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="168" formatCode="[$-10000455]0"/>
+    <numFmt numFmtId="164" formatCode="[$-10000455]0"/>
   </numFmts>
   <fonts count="1">
     <font>
